--- a/UserScore/MonthlyUserScore.xlsx
+++ b/UserScore/MonthlyUserScore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F904"/>
+  <dimension ref="A1:F905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23938,6 +23938,32 @@
         <v>1</v>
       </c>
     </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>904</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>7586891573</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>7586891573</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>@O000000000O00000000O</t>
+        </is>
+      </c>
+      <c r="E905" t="n">
+        <v>1</v>
+      </c>
+      <c r="F905" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/MonthlyUserScore.xlsx
+++ b/UserScore/MonthlyUserScore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F912"/>
+  <dimension ref="A1:F915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24146,6 +24146,84 @@
         <v>1</v>
       </c>
     </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>912</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>@BhaKth_bH0lenath_ka</t>
+        </is>
+      </c>
+      <c r="E913" t="n">
+        <v>8</v>
+      </c>
+      <c r="F913" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>913</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>-1002114430690</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>@BhaKth_bH0lenath_ka</t>
+        </is>
+      </c>
+      <c r="E914" t="n">
+        <v>6</v>
+      </c>
+      <c r="F914" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>914</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>-1002114430690</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>8495517533</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>@Graceful_by_mylord</t>
+        </is>
+      </c>
+      <c r="E915" t="n">
+        <v>3</v>
+      </c>
+      <c r="F915" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/MonthlyUserScore.xlsx
+++ b/UserScore/MonthlyUserScore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F915"/>
+  <dimension ref="A1:F916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24224,6 +24224,32 @@
         <v>2</v>
       </c>
     </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>915</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>-1002359766306</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>@BhaKth_bH0lenath_ka</t>
+        </is>
+      </c>
+      <c r="E916" t="n">
+        <v>3</v>
+      </c>
+      <c r="F916" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/MonthlyUserScore.xlsx
+++ b/UserScore/MonthlyUserScore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F603"/>
+  <dimension ref="A1:F605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16112,6 +16112,58 @@
         <v>1</v>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>@BhaKth_bH0lenath_ka</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>5</v>
+      </c>
+      <c r="F604" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>604</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-1002359766306</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>@BhaKth_bH0lenath_ka</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>2</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/MonthlyUserScore.xlsx
+++ b/UserScore/MonthlyUserScore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F534"/>
+  <dimension ref="A1:F629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>319</v>
+        <v>398</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
@@ -2166,14 +2166,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R💀</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F108" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109">
@@ -3362,14 +3362,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>प्रधानमंत्री</t>
+          <t>प्रधानमंत्री☻</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -3600,10 +3600,10 @@
         </is>
       </c>
       <c r="E122" t="n">
+        <v>3</v>
+      </c>
+      <c r="F122" t="n">
         <v>2</v>
-      </c>
-      <c r="F122" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="F126" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127">
@@ -3804,14 +3804,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>@Slientwolf_23</t>
+          <t>@Silentwolf_23</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162">
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F175" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F267" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="268">
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="F280" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="281">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -8488,10 +8488,10 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="F310" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311">
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315">
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F315" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="316">
@@ -8718,14 +8718,14 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>@ZENX407</t>
+          <t>@ZKNX407</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F319" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="320">
@@ -9004,14 +9004,14 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ㅤㅤ</t>
+          <t>ㅤㅤLluvia</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331">
@@ -9736,10 +9736,10 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F358" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="359">
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F365" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="366">
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F443" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="444">
@@ -12024,10 +12024,10 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -12154,10 +12154,10 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -13142,10 +13142,10 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F489" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="490">
@@ -13376,10 +13376,10 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -13428,10 +13428,10 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -13558,10 +13558,10 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506">
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F506" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="507">
@@ -13818,10 +13818,10 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F515" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="516">
@@ -13870,10 +13870,10 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F517" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="518">
@@ -14208,10 +14208,10 @@
         </is>
       </c>
       <c r="E530" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -14315,6 +14315,2476 @@
         <v>1</v>
       </c>
       <c r="F534" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-1002274964696</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>7490311932</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>@Code90875</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>6</v>
+      </c>
+      <c r="F535" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-1002274964696</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>8485456991</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>S M</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>1</v>
+      </c>
+      <c r="F536" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-1002832167728</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>8163718583</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>@Enstein1</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>5</v>
+      </c>
+      <c r="F537" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-1002392635902</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>1706884580</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Srishtii</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>17</v>
+      </c>
+      <c r="F538" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-1003500481482</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>7500406515</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Pooja</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>7</v>
+      </c>
+      <c r="F539" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-1002392635902</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>6208206438</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>@siyaram19114101141</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>1</v>
+      </c>
+      <c r="F540" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-1002864485836</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>7196602879</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Ake</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>1</v>
+      </c>
+      <c r="F541" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-1002761573267</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>8239976695</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>⏤͟͞𝘿𝑰𝙇⥴</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>2</v>
+      </c>
+      <c r="F542" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>1178749298</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>@S_Uptgt_A</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>26</v>
+      </c>
+      <c r="F543" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>822660029</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Baljeet saroj</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>14</v>
+      </c>
+      <c r="F544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>8544203846</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Adiba</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>10</v>
+      </c>
+      <c r="F545" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>1700557317</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Shubham</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>5</v>
+      </c>
+      <c r="F546" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-1002832167728</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>7593031262</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>@Theeagle0103</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>7</v>
+      </c>
+      <c r="F547" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>1152488065</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Gitanjali</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>2</v>
+      </c>
+      <c r="F548" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>8486201599</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>1</v>
+      </c>
+      <c r="F549" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-1002324412075</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>1191142204</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>@Onearth_17</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>12</v>
+      </c>
+      <c r="F550" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-1002324412075</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2111300890</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>@Mahesh_nalegavkar</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>2</v>
+      </c>
+      <c r="F551" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-1002591852942</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>7256006698</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>@White_Python02</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>2</v>
+      </c>
+      <c r="F552" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>8039925751</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>@Moonlightglint</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>138</v>
+      </c>
+      <c r="F553" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>5567356810</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>🎃</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>38</v>
+      </c>
+      <c r="F554" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>1700483709</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>mೀ</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>27</v>
+      </c>
+      <c r="F555" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>6688406027</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>6688406027</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>16</v>
+      </c>
+      <c r="F556" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-1003739476321</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>7780995268</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>anshika</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>7</v>
+      </c>
+      <c r="F557" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-1002947162126</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>6941860790</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>@rezowastaken</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>3</v>
+      </c>
+      <c r="F558" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-1001921955585</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>8467012450</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>@silentt001</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>35</v>
+      </c>
+      <c r="F559" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-1001921955585</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>926885240</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>@Mkanim</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>7</v>
+      </c>
+      <c r="F560" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>6614049023</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>@Jhontestic</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>175</v>
+      </c>
+      <c r="F561" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>7818516092</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>@i4SRK</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>82</v>
+      </c>
+      <c r="F562" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>8595811609</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>alexa</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>19</v>
+      </c>
+      <c r="F563" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>6616301546</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>@Ayaanuuu</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>1</v>
+      </c>
+      <c r="F564" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-1002360283286</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>8407130100</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>🖤</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>1</v>
+      </c>
+      <c r="F565" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-1003027038967</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>6534910347</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Simran</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>29</v>
+      </c>
+      <c r="F566" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-1003027038967</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>6451057512</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>.🥀🥀𝕶𝖎𝖓𝖌𝕾 Ñ𝖆𝖜𝖆𝖇</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>27</v>
+      </c>
+      <c r="F567" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-1003027038967</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>8319859774</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>👨‍🦳</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>15</v>
+      </c>
+      <c r="F568" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-1003027038967</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>6335581860</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>@coolmitraaa</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>26</v>
+      </c>
+      <c r="F569" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-1002274964696</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>8540894047</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Jennie</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>7</v>
+      </c>
+      <c r="F570" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-1002335271770</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>768495083</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>@ScorpioAA</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>9</v>
+      </c>
+      <c r="F571" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-1002579055686</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>6129870148</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>⋆─፝─᪵།‌꯭𝗦꯭ᴋ꯭ 𝗞꯭ʜ꯭ᴀ꯭ɴ꯭ ا۬͢𝆺𝅥⃝🌸𝄄꯭꯭𝄄꯭꯭ ̶꯭𝅥ͦ𝆬👑</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>3</v>
+      </c>
+      <c r="F572" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-1002579055686</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>7076814003</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>...Fatima</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>4</v>
+      </c>
+      <c r="F573" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-1002579055686</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>5188971199</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>@Ershabaz</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>1</v>
+      </c>
+      <c r="F574" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-1001298208876</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>1708309288</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Shruti</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>4</v>
+      </c>
+      <c r="F575" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-1002454558597</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>1708309288</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Shruti</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>9</v>
+      </c>
+      <c r="F576" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>-1003205119561</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>595208871</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>@Swtysanu</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>9</v>
+      </c>
+      <c r="F577" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>-1002815867232</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>8055407291</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>@Lj_beya</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>14</v>
+      </c>
+      <c r="F578" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-1002815867232</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>6842747291</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>@solishine</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>10</v>
+      </c>
+      <c r="F579" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>-1002815867232</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>8003258528</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>@Itsmrlone</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>1</v>
+      </c>
+      <c r="F580" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>-1002623818368</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>7548620409</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Wengelawit</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>5</v>
+      </c>
+      <c r="F581" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>-1002623818368</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>8064930457</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>@Hbub03</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>5</v>
+      </c>
+      <c r="F582" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>-1002268045818</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>738954475</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>@GodsArchimime</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>22</v>
+      </c>
+      <c r="F583" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>583</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>-1003169930553</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>7970136847</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>@Vikramjiiii</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>12</v>
+      </c>
+      <c r="F584" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>584</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>7744224715</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Anup</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>1</v>
+      </c>
+      <c r="F585" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>585</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>5007054449</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Nitin</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>46</v>
+      </c>
+      <c r="F586" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>586</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>6926199449</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>$hubham</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>98</v>
+      </c>
+      <c r="F587" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>587</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>7002090626</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>@Tk_18_7</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>8</v>
+      </c>
+      <c r="F588" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>588</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-1003050031260</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>7995157994</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>@Hm_mm_mm_mm</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>1</v>
+      </c>
+      <c r="F589" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>589</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-1002815867232</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>7935709070</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Lidiya</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>4</v>
+      </c>
+      <c r="F590" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>590</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-1002464524981</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>6916393853</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>R.M.</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>34</v>
+      </c>
+      <c r="F591" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>591</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-1003205119561</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>1288187246</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Sumitha</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>12</v>
+      </c>
+      <c r="F592" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>592</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>-1002591852942</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>6387945795</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>@Ramji_45</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>8</v>
+      </c>
+      <c r="F593" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>593</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-1003704472568</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>8535050029</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>°♡✧*𝙰𝚗𝐣𝗮ไ𝐢ⴽ𝗮𝐣ᴘᶶ𝙩*✧♡°</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>5</v>
+      </c>
+      <c r="F594" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>594</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-1003841442683</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>6192653010</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>@Madda_7738</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>14</v>
+      </c>
+      <c r="F595" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>595</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>-1002092120695</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>6415601180</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>@ara_entha</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>11</v>
+      </c>
+      <c r="F596" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>596</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-1002092120695</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>1971125096</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>@Yxmonk</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>2</v>
+      </c>
+      <c r="F597" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>597</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-1002092120695</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>1069690952</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>@Azy_1111</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>1</v>
+      </c>
+      <c r="F598" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>598</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-1003415576816</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>6415001739</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>@DRAGONGG69</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>7</v>
+      </c>
+      <c r="F599" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>599</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-1002011515239</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>1583562205</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>@POONNAAMM1</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>2</v>
+      </c>
+      <c r="F600" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>600</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-1002011515239</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>8166992419</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>@Krissshnaaaaa</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>1</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>601</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-1003759164664</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>5441086473</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Bizuye</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>1</v>
+      </c>
+      <c r="F602" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>602</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>-1002011515239</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>5758636613</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Sham Sunder</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>1</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>-1002011515239</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>7350101607</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>@Kittu_400</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>1</v>
+      </c>
+      <c r="F604" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>604</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-1002551279375</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>8594934883</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>@Athenaa_a_a</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>10</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-1003782057933</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>775071577</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>A.Narendra</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>10</v>
+      </c>
+      <c r="F606" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>-1003782057933</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>8492689255</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>@KAUSHIK194199</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>6</v>
+      </c>
+      <c r="F607" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>-1002623818368</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>6025980216</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>@Maryam_mariyam21</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>2</v>
+      </c>
+      <c r="F608" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-1002623818368</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>7498287756</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>@Originality340</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>1</v>
+      </c>
+      <c r="F609" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-1001900924039</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>7644983632</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>@itzmechan2129</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>6</v>
+      </c>
+      <c r="F610" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-1002393739109</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>7865641753</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>@itzahemyu</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>5</v>
+      </c>
+      <c r="F611" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-1002591852942</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>7760972147</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Sakshi 💗</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>1</v>
+      </c>
+      <c r="F612" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-1003628737566</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>7771700202</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>@SY_216</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>31</v>
+      </c>
+      <c r="F613" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-1003628737566</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>7867612857</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Shantanu singh</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>23</v>
+      </c>
+      <c r="F614" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-1003635435133</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>6544051816</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>𝙅𝙮𝙤𝙩𝙞</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>14</v>
+      </c>
+      <c r="F615" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-1002392635902</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>1146399530</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>🎖️BHOLANATH🎖️</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>6</v>
+      </c>
+      <c r="F616" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-1002011515239</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>8609773919</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>16</v>
+      </c>
+      <c r="F617" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-1002011515239</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>8186260552</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>সৰাপাত 🍂</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>1</v>
+      </c>
+      <c r="F618" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>618</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-1002360283286</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>6126725248</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>@Jaat_0_0_0_1</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>20</v>
+      </c>
+      <c r="F619" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>619</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-1002360283286</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>8429070304</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>✧𝙆𝙪𝙠𝙠𝙪✧</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>31</v>
+      </c>
+      <c r="F620" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>620</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-1002360283286</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>8365592349</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Ꮩɪᴋʀᴀᴍ Sᴏʟᴀɴᴋɪ</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>3</v>
+      </c>
+      <c r="F621" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>621</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-1001690032632</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>1164582001</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>@gazipoet</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>5</v>
+      </c>
+      <c r="F622" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>622</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-1001818742779</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>6178429465</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>MOHAMMAD</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>1</v>
+      </c>
+      <c r="F623" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>623</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-1002983071868</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>8444294197</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Heru</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>1</v>
+      </c>
+      <c r="F624" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>624</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-1002983071868</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>6628599769</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>@sxmn_12</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>5</v>
+      </c>
+      <c r="F625" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>625</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-1003881956622</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>8467852983</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Mhide</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>13</v>
+      </c>
+      <c r="F626" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>626</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-1003881956622</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>8388047255</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Felicia</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>8</v>
+      </c>
+      <c r="F627" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>627</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-1003881956622</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>8273997669</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>@otitopepro</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>13</v>
+      </c>
+      <c r="F628" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>628</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-1003881956622</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>7836986064</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>@Obi_Unfiltered</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>11</v>
+      </c>
+      <c r="F629" t="n">
         <v>1</v>
       </c>
     </row>
